--- a/docs/Smeta_2026-MOS40.xlsx
+++ b/docs/Smeta_2026-MOS40.xlsx
@@ -3121,28 +3121,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D0. Первоочередное</t>
+          <t>D0. Первоочередное (план 2026-МОС40-ПМ)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ограждение и знаки, разборка аварийной площадки, лоток по краю двора с подключением водостоков и закрытым выпуском, простые геодезические наблюдения за марками</t>
+          <t>отвод воды с крыш и двора (коллектор и закрытый выпуск), разборка аварийной площадки, ограждение на винтовых сваях, реперы, марки, маяки, наблюдательные скважины; стоимость — по плану 2026-МОС40-ПМ</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>не меняется заметно; уменьшается приток воды с двора и крыш</t>
+          <t>весной ориентировочно не опускается до 0,87–0,97</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>склон остаётся аварийным</t>
+          <t>склон остаётся аварийным (ниже нормы 1,15)</t>
         </is>
       </c>
     </row>

--- a/docs/Smeta_2026-MOS40.xlsx
+++ b/docs/Smeta_2026-MOS40.xlsx
@@ -3121,28 +3121,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D0. Первоочередное (план 2026-МОС40-ПМ)</t>
+          <t>D0. Первоочередное</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>отвод воды с крыш и двора (коллектор и закрытый выпуск), разборка аварийной площадки, ограждение на винтовых сваях, реперы, марки, маяки, наблюдательные скважины; стоимость — по плану 2026-МОС40-ПМ</t>
+          <t>ограждение и знаки, разборка аварийной площадки, лоток по краю двора с подключением водостоков и закрытым выпуском, простые геодезические наблюдения за марками</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>весной ориентировочно не опускается до 0,87–0,97</t>
+          <t>не меняется заметно; уменьшается приток воды с двора и крыш</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>склон остаётся аварийным (ниже нормы 1,15)</t>
+          <t>склон остаётся аварийным</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>весной запас не опускается до 0,87–0,97, остаётся ≈ 0,93–1,01</t>
+          <t>весной запас не опускается до 0,83–0,97, остаётся ≈ 0,90–1,01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
